--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14331,7 +14331,7 @@
         <v>117482518</v>
       </c>
       <c r="B118" t="n">
-        <v>94339</v>
+        <v>94341</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12007,12 +12007,7 @@
         <v>96955832</v>
       </c>
       <c r="B99" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5196</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12051,10 +12046,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>578150.8168496353</v>
+        <v>578150</v>
       </c>
       <c r="R99" t="n">
-        <v>6707447.044796604</v>
+        <v>6707447</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12007,7 +12007,7 @@
         <v>96955832</v>
       </c>
       <c r="B99" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY118"/>
+  <dimension ref="A1:AY121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14433,6 +14433,297 @@
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>127698737</v>
+      </c>
+      <c r="B119" t="n">
+        <v>97127</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>578203</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6707455</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127698986</v>
+      </c>
+      <c r="B120" t="n">
+        <v>95690</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>578203</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6707455</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>127701361</v>
+      </c>
+      <c r="B121" t="n">
+        <v>97138</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>2609</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Blåsfliksmossa</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Lejeunea cavifolia</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>578203</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6707455</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97127</v>
+        <v>97129</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95690</v>
+        <v>95692</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97138</v>
+        <v>97140</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97129</v>
+        <v>97135</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95692</v>
+        <v>95698</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97140</v>
+        <v>97146</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97135</v>
+        <v>97138</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95698</v>
+        <v>95701</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97146</v>
+        <v>97149</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97138</v>
+        <v>97146</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95701</v>
+        <v>95709</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97149</v>
+        <v>97157</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97146</v>
+        <v>97147</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95709</v>
+        <v>95710</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97157</v>
+        <v>97158</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97147</v>
+        <v>97148</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95710</v>
+        <v>95711</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97158</v>
+        <v>97159</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97148</v>
+        <v>97149</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95711</v>
+        <v>95712</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97159</v>
+        <v>97160</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97149</v>
+        <v>97157</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95712</v>
+        <v>95720</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97160</v>
+        <v>97168</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -14438,7 +14438,7 @@
         <v>127698737</v>
       </c>
       <c r="B119" t="n">
-        <v>97157</v>
+        <v>97169</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>127698986</v>
       </c>
       <c r="B120" t="n">
-        <v>95720</v>
+        <v>95732</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>127701361</v>
       </c>
       <c r="B121" t="n">
-        <v>97168</v>
+        <v>97180</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,12 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98579</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12272,10 +12267,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>578287.1663024784</v>
+        <v>578287</v>
       </c>
       <c r="R101" t="n">
-        <v>6707465.766767904</v>
+        <v>6707466</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -12305,19 +12300,9 @@
           <t>2000-05-06</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2000-05-06</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12361,12 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109149</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12398,10 +12378,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>578354.2944003863</v>
+        <v>578354</v>
       </c>
       <c r="R102" t="n">
-        <v>6707625.928503646</v>
+        <v>6707626</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12431,19 +12411,9 @@
           <t>2000-07-01</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2000-07-01</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12487,12 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98579</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12524,10 +12489,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>578266.0461773539</v>
+        <v>578266</v>
       </c>
       <c r="R103" t="n">
-        <v>6707483.546523334</v>
+        <v>6707484</v>
       </c>
       <c r="S103" t="n">
         <v>100</v>
@@ -12557,19 +12522,9 @@
           <t>1987-08-11</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>1987-08-11</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12613,12 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12650,10 +12600,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>578266.0461773539</v>
+        <v>578266</v>
       </c>
       <c r="R104" t="n">
-        <v>6707483.546523334</v>
+        <v>6707484</v>
       </c>
       <c r="S104" t="n">
         <v>100</v>
@@ -12683,19 +12633,9 @@
           <t>1987-08-11</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>1987-08-11</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12739,12 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>97034</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99314</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12776,10 +12711,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>578093.2127299515</v>
+        <v>578093</v>
       </c>
       <c r="R105" t="n">
-        <v>6707462.558627083</v>
+        <v>6707463</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12809,19 +12744,9 @@
           <t>2010-06-17</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2010-06-17</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109149</v>
+        <v>109158</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99314</v>
+        <v>99320</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109158</v>
+        <v>109171</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99320</v>
+        <v>99323</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99329</v>
+        <v>99356</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99356</v>
+        <v>99362</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99362</v>
+        <v>99369</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14649,6 +14649,113 @@
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128912117</v>
+      </c>
+      <c r="B122" t="n">
+        <v>97305</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Åstjärnen, Åstjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>578159</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6707470</v>
+      </c>
+      <c r="S122" t="n">
+        <v>9</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99369</v>
+        <v>99373</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>128912117</v>
       </c>
       <c r="B122" t="n">
-        <v>97305</v>
+        <v>97309</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2022 artfynd.xlsx
+++ b/artfynd/A 34616-2022 artfynd.xlsx
@@ -12235,7 +12235,7 @@
         <v>97093040</v>
       </c>
       <c r="B101" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>97093212</v>
       </c>
       <c r="B102" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>97408792</v>
       </c>
       <c r="B103" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>97408802</v>
       </c>
       <c r="B104" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>97423474</v>
       </c>
       <c r="B105" t="n">
-        <v>99373</v>
+        <v>99380</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>128912117</v>
       </c>
       <c r="B122" t="n">
-        <v>97309</v>
+        <v>97316</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
